--- a/output/北塩原村_目標KPI_前回比較可能性.xlsx
+++ b/output/北塩原村_目標KPI_前回比較可能性.xlsx
@@ -4033,7 +4033,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>村に照会する（見込量算定 M-4・リスクR-25）。給付実績に計上漏れがある場合、第8期の見込量と給付費の基準が変わる</t>
+          <t>村に照会する（見込量算定 Ｍ-4・リスクR-25）。給付実績に計上漏れがある場合、第8期の見込量と給付費の基準が変わる</t>
         </is>
       </c>
     </row>
